--- a/output/2026-10-05_17_Croazia_Dubrovacko-neretvanska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-10-05_17_Croazia_Dubrovacko-neretvanska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Šipčine 10, 20000 Dubrovnik. Rivenditore ufficiale Bosch Professional; vendita/noleggio/servizio utensili elettrici e pneumatici (Bosch, Metabo, Makita, Flex, Wolfcraft, Dremel, Proxxon, Hilti, Telwin, Comet). Registrato anche per ingrosso/dettaglio ferramenta (46.84.0, 47.52.0). Fonti: fininfo.hr, mojkvart.hr, tvrtke.hr, nicelocal.com.hr.</t>
+          <t>Šipčine 10, 20000 Dubrovnik. Rivenditore ufficiale Bosch Professional; vendita/noleggio/servizio utensili elettrici e pneumatici (Bosch, Metabo, Makita, Flex, Wolfcraft, Dremel, Proxxon, Hilti, Telwin, Comet). Registrato anche per ingrosso/dettaglio ferramenta (46.84.0, 47.52.0). Fonti: fininfo.hr, mojkvart.hr, tvrtke.hr, nicelocal.com.hr. [DUPLICATO — vedi anche: 2026-09-21_00_Croazia_Dubrovačko-neretvanska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
